--- a/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
+++ b/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\chrisbyrd-esp32iotproduct\Design Files\Ethernet-Module-v2.0\Ethernet-Module-v2.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\chrisbyrd-esp32iotproduct\Design Files\Ethernet-Module-v2.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="176">
   <si>
     <t>Component list</t>
   </si>
@@ -105,9 +105,6 @@
     <t>J1</t>
   </si>
   <si>
-    <t>J3</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -189,9 +186,6 @@
     <t>RES SMD 1K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES SMD 10K OHM 5% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES SMD 0R, 1%, 0.1W, 0603</t>
   </si>
   <si>
@@ -231,9 +225,6 @@
     <t>IND-1210</t>
   </si>
   <si>
-    <t>ARJM11C7-114-BA-EW2</t>
-  </si>
-  <si>
     <t>SOT-723</t>
   </si>
   <si>
@@ -291,9 +282,6 @@
     <t>RC0603FR-071KL</t>
   </si>
   <si>
-    <t>AC0603JR-0710KL</t>
-  </si>
-  <si>
     <t>RC0603FR-070RL</t>
   </si>
   <si>
@@ -339,208 +327,226 @@
     <t>Taiyo Yuden</t>
   </si>
   <si>
+    <t>TECH PUBLIC</t>
+  </si>
+  <si>
+    <t>ON Semiconductor / Fairchild</t>
+  </si>
+  <si>
+    <t>WIZNET</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t>NDK</t>
+  </si>
+  <si>
+    <t>LCSC Part Number</t>
+  </si>
+  <si>
+    <t>C109447</t>
+  </si>
+  <si>
+    <t>C110022</t>
+  </si>
+  <si>
+    <t>C2168289</t>
+  </si>
+  <si>
+    <t>C1631</t>
+  </si>
+  <si>
+    <t>C149602</t>
+  </si>
+  <si>
+    <t>C76615</t>
+  </si>
+  <si>
+    <t>C268004</t>
+  </si>
+  <si>
+    <t>C2923360</t>
+  </si>
+  <si>
+    <t>C725031</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>C100044</t>
+  </si>
+  <si>
+    <t>C114625</t>
+  </si>
+  <si>
+    <t>C109318</t>
+  </si>
+  <si>
+    <t>C108661</t>
+  </si>
+  <si>
+    <t>C105879</t>
+  </si>
+  <si>
+    <t>C105578</t>
+  </si>
+  <si>
+    <t>C137798</t>
+  </si>
+  <si>
+    <t>C32843</t>
+  </si>
+  <si>
+    <t>C10675</t>
+  </si>
+  <si>
+    <t>C438901</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>0.1uF</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>6.8nF</t>
+  </si>
+  <si>
+    <t>22nF</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>12pF</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t>49.9R</t>
+  </si>
+  <si>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>33R</t>
+  </si>
+  <si>
+    <t>330R</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>12.4K</t>
+  </si>
+  <si>
+    <t>25MHZ</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Alternate Part Number</t>
+  </si>
+  <si>
+    <t>Quantity (5 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (5 Boards)</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Unit Cost (5 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (5 Boards)</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Reviewer Remarks</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini PCIe SMD Pad </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>Ethernet-Module-v2.0.</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [Ethernet-Module-v2.0.]</t>
+  </si>
+  <si>
+    <t>R2, R9, R12, R17, R18, R19, R22, R23, R24, R25, R26, R27, R29, R30, R31, R32</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>RES SMD 10K OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
+    <t>Res-0201</t>
+  </si>
+  <si>
+    <t>RC0201FR-0710KL</t>
+  </si>
+  <si>
+    <t>C106225</t>
+  </si>
+  <si>
+    <t>C426087</t>
+  </si>
+  <si>
+    <t>0603N120J101CT</t>
+  </si>
+  <si>
+    <t>C3858995</t>
+  </si>
+  <si>
+    <t>CONN JACK 1PORT 100 BASE-T PCB</t>
+  </si>
+  <si>
+    <t>ARJM11D7-114-AB-EW2</t>
+  </si>
+  <si>
     <t>Abracon</t>
   </si>
   <si>
-    <t>TECH PUBLIC</t>
-  </si>
-  <si>
-    <t>ON Semiconductor / Fairchild</t>
-  </si>
-  <si>
-    <t>WIZNET</t>
-  </si>
-  <si>
-    <t>Littelfuse</t>
-  </si>
-  <si>
-    <t>NDK</t>
-  </si>
-  <si>
-    <t>LCSC Part Number</t>
-  </si>
-  <si>
-    <t>C109447</t>
-  </si>
-  <si>
-    <t>C110022</t>
-  </si>
-  <si>
-    <t>C2168289</t>
-  </si>
-  <si>
-    <t>C1631</t>
-  </si>
-  <si>
-    <t>C2167165</t>
-  </si>
-  <si>
-    <t>C149602</t>
-  </si>
-  <si>
-    <t>C76615</t>
-  </si>
-  <si>
-    <t>C701298</t>
-  </si>
-  <si>
-    <t>C268004</t>
-  </si>
-  <si>
-    <t>C2923360</t>
-  </si>
-  <si>
-    <t>C725031</t>
-  </si>
-  <si>
-    <t>C22548</t>
-  </si>
-  <si>
-    <t>C140867</t>
-  </si>
-  <si>
-    <t>C100044</t>
-  </si>
-  <si>
-    <t>C114625</t>
-  </si>
-  <si>
-    <t>C109318</t>
-  </si>
-  <si>
-    <t>C108661</t>
-  </si>
-  <si>
-    <t>C105879</t>
-  </si>
-  <si>
-    <t>C105578</t>
-  </si>
-  <si>
-    <t>C137798</t>
-  </si>
-  <si>
-    <t>C32843</t>
-  </si>
-  <si>
-    <t>C10675</t>
-  </si>
-  <si>
-    <t>C438901</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>0.1uF</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>6.8nF</t>
-  </si>
-  <si>
-    <t>22nF</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>12pF</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>0R</t>
-  </si>
-  <si>
-    <t>49.9R</t>
-  </si>
-  <si>
-    <t>10R</t>
-  </si>
-  <si>
-    <t>33R</t>
-  </si>
-  <si>
-    <t>330R</t>
-  </si>
-  <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>12.4K</t>
-  </si>
-  <si>
-    <t>25MHZ</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Alternate Part Number</t>
-  </si>
-  <si>
-    <t>Quantity (5 Boards)</t>
-  </si>
-  <si>
-    <t>MOQ (5 Boards)</t>
-  </si>
-  <si>
-    <t>Links</t>
-  </si>
-  <si>
-    <t>Unit Cost (5 Boards)</t>
-  </si>
-  <si>
-    <t>Total Cost (5 Boards)</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Reviewer Remarks</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mini PCIe SMD Pad </t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>LCSC</t>
-  </si>
-  <si>
-    <t>DO NOT MOUNT</t>
-  </si>
-  <si>
-    <t>Ethernet-Module-v2.0.</t>
-  </si>
-  <si>
-    <t>Bill of Materials for Project [Ethernet-Module-v2.0.]</t>
-  </si>
-  <si>
-    <t>Digikey</t>
-  </si>
-  <si>
-    <t>CONN JACK 1PORT 100 BASE-T PCB</t>
-  </si>
-  <si>
-    <t>R2, R9, R12, R17, R18, R19, R22, R23, R24, R25, R26, R27, R29, R30, R31, R32</t>
+    <t>Mouser</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1027,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1226,9 +1232,29 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1624,7 +1650,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1649,7 +1675,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1674,7 +1700,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1790,49 +1816,49 @@
         <v>17</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>163</v>
-      </c>
       <c r="L9" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>154</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1848,25 +1874,25 @@
         <v>18</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="L10" s="37">
         <v>2</v>
@@ -1879,7 +1905,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P10" s="38">
         <v>3.5200000000000002E-2</v>
@@ -1904,25 +1930,25 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="L11" s="51">
         <v>7</v>
@@ -1935,7 +1961,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P11" s="52">
         <v>3.5999999999999999E-3</v>
@@ -1960,25 +1986,25 @@
         <v>20</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L12" s="37">
         <v>2</v>
@@ -1991,7 +2017,7 @@
         <v>11</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P12" s="38">
         <v>0.75260000000000005</v>
@@ -2016,25 +2042,25 @@
         <v>21</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="L13" s="51">
         <v>2</v>
@@ -2047,7 +2073,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P13" s="52">
         <v>2.8E-3</v>
@@ -2072,23 +2098,23 @@
         <v>22</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>82</v>
+        <v>66</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>79</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2097,14 +2123,18 @@
         <f>L14*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="P14" s="38"/>
+      <c r="N14" s="37">
+        <v>50</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="P14" s="38">
+        <v>1.5800000000000002E-2</v>
+      </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
@@ -2122,25 +2152,25 @@
         <v>23</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -2153,7 +2183,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P15" s="52">
         <v>7.4000000000000003E-3</v>
@@ -2178,25 +2208,25 @@
         <v>24</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -2209,7 +2239,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P16" s="38">
         <v>4.2299999999999997E-2</v>
@@ -2234,23 +2264,25 @@
         <v>25</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>85</v>
+        <v>66</v>
+      </c>
+      <c r="G17" s="63" t="s">
+        <v>82</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="51"/>
+        <v>100</v>
+      </c>
+      <c r="I17" s="51" t="s">
+        <v>170</v>
+      </c>
       <c r="J17" s="51" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2259,14 +2291,18 @@
         <f t="shared" ref="M17" si="7">L17*5</f>
         <v>10</v>
       </c>
-      <c r="N17" s="51"/>
-      <c r="O17" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="P17" s="52"/>
+      <c r="N17" s="51">
+        <v>100</v>
+      </c>
+      <c r="O17" s="60" t="s">
+        <v>159</v>
+      </c>
+      <c r="P17" s="52">
+        <v>5.7999999999999996E-3</v>
+      </c>
       <c r="Q17" s="52">
         <f t="shared" ref="Q17" si="8">P17*N17</f>
-        <v>0</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
@@ -2284,25 +2320,25 @@
         <v>26</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L18" s="37">
         <v>2</v>
@@ -2315,7 +2351,7 @@
         <v>15</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P18" s="38">
         <v>0.18790000000000001</v>
@@ -2327,57 +2363,61 @@
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="47">
+    <row r="19" spans="1:19" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="74"/>
+      <c r="B19" s="75">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="74" t="s">
+      <c r="E19" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="L19" s="51">
+      <c r="F19" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="J19" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="K19" s="78" t="s">
+        <v>158</v>
+      </c>
+      <c r="L19" s="77">
         <v>1</v>
       </c>
-      <c r="M19" s="51">
+      <c r="M19" s="77">
         <f t="shared" ref="M19" si="9">L19*5</f>
         <v>5</v>
       </c>
-      <c r="N19" s="51">
+      <c r="N19" s="77">
         <v>6</v>
       </c>
-      <c r="O19" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="P19" s="52">
-        <v>3.46</v>
-      </c>
-      <c r="Q19" s="52">
+      <c r="O19" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="P19" s="80">
+        <v>3.47</v>
+      </c>
+      <c r="Q19" s="80">
         <f t="shared" ref="Q19" si="10">P19*N19</f>
-        <v>20.759999999999998</v>
-      </c>
-      <c r="R19" s="51"/>
-      <c r="S19" s="59"/>
+        <v>20.82</v>
+      </c>
+      <c r="R19" s="77"/>
+      <c r="S19" s="81"/>
     </row>
     <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2386,31 +2426,31 @@
         <v>11</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="E20" s="63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20" s="63" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L20" s="63">
         <v>1</v>
@@ -2420,19 +2460,19 @@
         <v>5</v>
       </c>
       <c r="N20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="O20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="P20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="Q20" s="63" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="R20" s="62" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="S20" s="59"/>
     </row>
@@ -2446,28 +2486,28 @@
         <v>12</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2480,7 +2520,7 @@
         <v>20</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P21" s="52">
         <v>3.3500000000000002E-2</v>
@@ -2502,28 +2542,28 @@
         <v>12</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2536,7 +2576,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P22" s="38">
         <v>7.3700000000000002E-2</v>
@@ -2558,28 +2598,28 @@
         <v>13</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="L23" s="51">
         <v>1</v>
@@ -2592,7 +2632,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P23" s="52">
         <v>1E-3</v>
@@ -2614,28 +2654,28 @@
         <v>13</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="L24" s="37">
         <v>16</v>
@@ -2648,14 +2688,14 @@
         <v>100</v>
       </c>
       <c r="O24" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P24" s="52">
-        <v>1E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -2670,28 +2710,28 @@
         <v>13</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="L25" s="51">
         <v>2</v>
@@ -2704,7 +2744,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P25" s="52">
         <v>1.2999999999999999E-3</v>
@@ -2726,28 +2766,28 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="L26" s="37">
         <v>4</v>
@@ -2760,7 +2800,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P26" s="38">
         <v>1.1999999999999999E-3</v>
@@ -2782,28 +2822,28 @@
         <v>13</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -2816,7 +2856,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P27" s="52">
         <v>3.2000000000000002E-3</v>
@@ -2838,28 +2878,28 @@
         <v>13</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="L28" s="37">
         <v>4</v>
@@ -2872,7 +2912,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P28" s="38">
         <v>1.1999999999999999E-3</v>
@@ -2894,28 +2934,28 @@
         <v>13</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="L29" s="51">
         <v>2</v>
@@ -2928,7 +2968,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P29" s="52">
         <v>1.1000000000000001E-3</v>
@@ -2950,28 +2990,28 @@
         <v>13</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -2984,7 +3024,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P30" s="38">
         <v>1.2999999999999999E-3</v>
@@ -3006,28 +3046,28 @@
         <v>13</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G31" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="H31" s="51" t="s">
-        <v>101</v>
-      </c>
       <c r="I31" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="L31" s="51">
         <v>1</v>
@@ -3040,7 +3080,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P31" s="52">
         <v>1.1999999999999999E-3</v>
@@ -3062,28 +3102,28 @@
         <v>14</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I32" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3096,7 +3136,7 @@
         <v>6</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P32" s="38">
         <v>2.641</v>
@@ -3118,28 +3158,28 @@
         <v>15</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -3152,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P33" s="52">
         <v>0.56479999999999997</v>
@@ -3174,28 +3214,28 @@
         <v>16</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="L34" s="37">
         <v>1</v>
@@ -3208,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P34" s="38">
         <v>0.25240000000000001</v>
@@ -3241,7 +3281,7 @@
       <c r="P35" s="73"/>
       <c r="Q35" s="48">
         <f>SUM(Q10:Q34)</f>
-        <v>57.770300000000013</v>
+        <v>59.190300000000015</v>
       </c>
       <c r="R35" s="68"/>
       <c r="S35" s="69"/>
@@ -3267,7 +3307,7 @@
       <c r="P36" s="73"/>
       <c r="Q36" s="49">
         <f>Q35/5</f>
-        <v>11.554060000000003</v>
+        <v>11.838060000000002</v>
       </c>
       <c r="R36" s="70"/>
       <c r="S36" s="71"/>
@@ -3291,21 +3331,23 @@
     <hyperlink ref="O21" r:id="rId8"/>
     <hyperlink ref="O22" r:id="rId9"/>
     <hyperlink ref="O23" r:id="rId10"/>
-    <hyperlink ref="O24" r:id="rId11"/>
-    <hyperlink ref="O25" r:id="rId12"/>
-    <hyperlink ref="O26" r:id="rId13"/>
-    <hyperlink ref="O27" r:id="rId14"/>
-    <hyperlink ref="O28" r:id="rId15"/>
-    <hyperlink ref="O29" r:id="rId16"/>
-    <hyperlink ref="O30" r:id="rId17"/>
-    <hyperlink ref="O31" r:id="rId18"/>
-    <hyperlink ref="O32" r:id="rId19"/>
-    <hyperlink ref="O33" r:id="rId20"/>
-    <hyperlink ref="O34" r:id="rId21"/>
-    <hyperlink ref="O19" r:id="rId22"/>
+    <hyperlink ref="O25" r:id="rId11"/>
+    <hyperlink ref="O26" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O28" r:id="rId14"/>
+    <hyperlink ref="O29" r:id="rId15"/>
+    <hyperlink ref="O30" r:id="rId16"/>
+    <hyperlink ref="O31" r:id="rId17"/>
+    <hyperlink ref="O32" r:id="rId18"/>
+    <hyperlink ref="O33" r:id="rId19"/>
+    <hyperlink ref="O34" r:id="rId20"/>
+    <hyperlink ref="O14" r:id="rId21"/>
+    <hyperlink ref="O17" r:id="rId22"/>
+    <hyperlink ref="O24" r:id="rId23"/>
+    <hyperlink ref="O19" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
-  <drawing r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
+  <drawing r:id="rId26"/>
 </worksheet>
 </file>
--- a/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
+++ b/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
@@ -114,9 +114,6 @@
     <t>R1</t>
   </si>
   <si>
-    <t>R3, R21</t>
-  </si>
-  <si>
     <t>R4, R5, R15, R16</t>
   </si>
   <si>
@@ -510,9 +507,6 @@
     <t>Bill of Materials for Project [Ethernet-Module-v2.0.]</t>
   </si>
   <si>
-    <t>R2, R9, R12, R17, R18, R19, R22, R23, R24, R25, R26, R27, R29, R30, R31, R32</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
@@ -547,6 +541,12 @@
   </si>
   <si>
     <t>Mouser</t>
+  </si>
+  <si>
+    <t>R2, R9, R12, R17, R18, R19, R22, R23, R24, R25, R26, R27</t>
+  </si>
+  <si>
+    <t>R3, R21, R29</t>
   </si>
 </sst>
 </file>
@@ -1200,6 +1200,29 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1232,29 +1255,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1631,15 +1631,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="65"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="74"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1689,7 +1689,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="66"/>
+      <c r="S3" s="75"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1714,7 +1714,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="67"/>
+      <c r="S4" s="76"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1739,7 +1739,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="67"/>
+      <c r="S5" s="76"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1760,7 +1760,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="67"/>
+      <c r="S6" s="76"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1781,7 +1781,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="67"/>
+      <c r="S7" s="76"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1802,7 +1802,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="67"/>
+      <c r="S8" s="76"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1816,49 +1816,49 @@
         <v>17</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>153</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1874,25 +1874,25 @@
         <v>18</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10" s="37">
         <v>2</v>
@@ -1905,7 +1905,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P10" s="38">
         <v>3.5200000000000002E-2</v>
@@ -1930,25 +1930,25 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L11" s="51">
         <v>7</v>
@@ -1961,7 +1961,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P11" s="52">
         <v>3.5999999999999999E-3</v>
@@ -1986,25 +1986,25 @@
         <v>20</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L12" s="37">
         <v>2</v>
@@ -2017,7 +2017,7 @@
         <v>11</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P12" s="38">
         <v>0.75260000000000005</v>
@@ -2042,25 +2042,25 @@
         <v>21</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L13" s="51">
         <v>2</v>
@@ -2073,7 +2073,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P13" s="52">
         <v>2.8E-3</v>
@@ -2098,23 +2098,23 @@
         <v>22</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2127,7 +2127,7 @@
         <v>50</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P14" s="38">
         <v>1.5800000000000002E-2</v>
@@ -2152,25 +2152,25 @@
         <v>23</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -2183,7 +2183,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P15" s="52">
         <v>7.4000000000000003E-3</v>
@@ -2208,25 +2208,25 @@
         <v>24</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -2239,7 +2239,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P16" s="38">
         <v>4.2299999999999997E-2</v>
@@ -2264,25 +2264,25 @@
         <v>25</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2295,7 +2295,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P17" s="52">
         <v>5.7999999999999996E-3</v>
@@ -2320,25 +2320,25 @@
         <v>26</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L18" s="37">
         <v>2</v>
@@ -2351,7 +2351,7 @@
         <v>15</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P18" s="38">
         <v>0.18790000000000001</v>
@@ -2363,61 +2363,61 @@
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" s="82" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="74"/>
-      <c r="B19" s="75">
+    <row r="19" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="64"/>
+      <c r="B19" s="65">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="77" t="s">
+      <c r="E19" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="G19" s="77" t="s">
-        <v>173</v>
-      </c>
-      <c r="H19" s="77" t="s">
-        <v>174</v>
-      </c>
-      <c r="I19" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="J19" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="K19" s="78" t="s">
-        <v>158</v>
-      </c>
-      <c r="L19" s="77">
+      <c r="I19" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="J19" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="K19" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="L19" s="67">
         <v>1</v>
       </c>
-      <c r="M19" s="77">
+      <c r="M19" s="67">
         <f t="shared" ref="M19" si="9">L19*5</f>
         <v>5</v>
       </c>
-      <c r="N19" s="77">
+      <c r="N19" s="67">
         <v>6</v>
       </c>
-      <c r="O19" s="79" t="s">
-        <v>175</v>
-      </c>
-      <c r="P19" s="80">
+      <c r="O19" s="69" t="s">
+        <v>173</v>
+      </c>
+      <c r="P19" s="70">
         <v>3.47</v>
       </c>
-      <c r="Q19" s="80">
+      <c r="Q19" s="70">
         <f t="shared" ref="Q19" si="10">P19*N19</f>
         <v>20.82</v>
       </c>
-      <c r="R19" s="77"/>
-      <c r="S19" s="81"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="71"/>
     </row>
     <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2426,31 +2426,31 @@
         <v>11</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D20" s="63" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E20" s="63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F20" s="63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L20" s="63">
         <v>1</v>
@@ -2460,19 +2460,19 @@
         <v>5</v>
       </c>
       <c r="N20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q20" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R20" s="62" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S20" s="59"/>
     </row>
@@ -2489,25 +2489,25 @@
         <v>28</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2520,7 +2520,7 @@
         <v>20</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P21" s="52">
         <v>3.3500000000000002E-2</v>
@@ -2545,25 +2545,25 @@
         <v>29</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2576,7 +2576,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P22" s="38">
         <v>7.3700000000000002E-2</v>
@@ -2601,25 +2601,25 @@
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L23" s="51">
         <v>1</v>
@@ -2632,7 +2632,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P23" s="52">
         <v>1E-3</v>
@@ -2644,7 +2644,7 @@
       <c r="R23" s="51"/>
       <c r="S23" s="59"/>
     </row>
-    <row r="24" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="46">
         <f>ROW(B24) - ROW($B$9)</f>
@@ -2654,41 +2654,41 @@
         <v>13</v>
       </c>
       <c r="D24" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="F24" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="G24" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="H24" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="J24" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="G24" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>168</v>
-      </c>
       <c r="K24" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L24" s="37">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M24" s="37">
         <f>L24*5</f>
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N24" s="37">
         <v>100</v>
       </c>
       <c r="O24" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P24" s="52">
         <v>8.9999999999999998E-4</v>
@@ -2710,41 +2710,41 @@
         <v>13</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L25" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M25" s="51">
         <f t="shared" ref="M25" si="15">L25*5</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N25" s="51">
         <v>100</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P25" s="52">
         <v>1.2999999999999999E-3</v>
@@ -2766,28 +2766,28 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L26" s="37">
         <v>4</v>
@@ -2800,7 +2800,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P26" s="38">
         <v>1.1999999999999999E-3</v>
@@ -2822,28 +2822,28 @@
         <v>13</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -2856,7 +2856,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P27" s="52">
         <v>3.2000000000000002E-3</v>
@@ -2878,28 +2878,28 @@
         <v>13</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L28" s="37">
         <v>4</v>
@@ -2912,7 +2912,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P28" s="38">
         <v>1.1999999999999999E-3</v>
@@ -2934,28 +2934,28 @@
         <v>13</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L29" s="51">
         <v>2</v>
@@ -2968,7 +2968,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P29" s="52">
         <v>1.1000000000000001E-3</v>
@@ -2990,28 +2990,28 @@
         <v>13</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3024,7 +3024,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P30" s="38">
         <v>1.2999999999999999E-3</v>
@@ -3046,28 +3046,28 @@
         <v>13</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L31" s="51">
         <v>1</v>
@@ -3080,7 +3080,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P31" s="52">
         <v>1.1999999999999999E-3</v>
@@ -3102,28 +3102,28 @@
         <v>14</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I32" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3136,7 +3136,7 @@
         <v>6</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P32" s="38">
         <v>2.641</v>
@@ -3158,28 +3158,28 @@
         <v>15</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -3192,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P33" s="52">
         <v>0.56479999999999997</v>
@@ -3214,28 +3214,28 @@
         <v>16</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L34" s="37">
         <v>1</v>
@@ -3248,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P34" s="38">
         <v>0.25240000000000001</v>
@@ -3274,17 +3274,17 @@
       <c r="K35" s="45"/>
       <c r="L35" s="45"/>
       <c r="M35" s="45"/>
-      <c r="N35" s="72" t="s">
+      <c r="N35" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="73"/>
-      <c r="P35" s="73"/>
+      <c r="O35" s="82"/>
+      <c r="P35" s="82"/>
       <c r="Q35" s="48">
         <f>SUM(Q10:Q34)</f>
         <v>59.190300000000015</v>
       </c>
-      <c r="R35" s="68"/>
-      <c r="S35" s="69"/>
+      <c r="R35" s="77"/>
+      <c r="S35" s="78"/>
     </row>
     <row r="36" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -3300,17 +3300,17 @@
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
       <c r="M36" s="10"/>
-      <c r="N36" s="72" t="s">
+      <c r="N36" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="O36" s="73"/>
-      <c r="P36" s="73"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
       <c r="Q36" s="49">
         <f>Q35/5</f>
         <v>11.838060000000002</v>
       </c>
-      <c r="R36" s="70"/>
-      <c r="S36" s="71"/>
+      <c r="R36" s="79"/>
+      <c r="S36" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
+++ b/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="182">
   <si>
     <t>Component list</t>
   </si>
@@ -547,6 +547,24 @@
   </si>
   <si>
     <t>R3, R21, R29</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>RES 4.7K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>Res-0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-074K7L</t>
+  </si>
+  <si>
+    <t>C105871</t>
+  </si>
+  <si>
+    <t>4.7K</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1615,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1920,7 +1938,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B33" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B34" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -3099,31 +3117,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="I32" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="I32" s="37" t="s">
         <v>157</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3133,192 +3151,248 @@
         <v>5</v>
       </c>
       <c r="N32" s="37">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="O32" s="60" t="s">
         <v>158</v>
       </c>
       <c r="P32" s="38">
-        <v>2.641</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>15.846</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="47">
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f>L33*5</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="37">
+        <v>6</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="P33" s="38">
+        <v>2.641</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>15.846</v>
+      </c>
+      <c r="R33" s="37"/>
+      <c r="S33" s="59"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="47">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C33" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="51" t="s">
+      <c r="D34" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="51" t="s">
+      <c r="E34" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F34" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="G33" s="51" t="s">
+      <c r="G34" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="51" t="s">
+      <c r="H34" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="I33" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J33" s="51" t="s">
+      <c r="I34" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="J34" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="K33" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="L33" s="51">
+      <c r="K34" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="L34" s="51">
         <v>1</v>
       </c>
-      <c r="M33" s="51">
-        <f t="shared" ref="M33" si="23">L33*5</f>
+      <c r="M34" s="51">
+        <f t="shared" ref="M34" si="23">L34*5</f>
         <v>5</v>
       </c>
-      <c r="N33" s="51">
+      <c r="N34" s="51">
         <v>6</v>
       </c>
-      <c r="O33" s="61" t="s">
+      <c r="O34" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="P33" s="52">
+      <c r="P34" s="52">
         <v>0.56479999999999997</v>
       </c>
-      <c r="Q33" s="52">
-        <f t="shared" ref="Q33" si="24">P33*N33</f>
+      <c r="Q34" s="52">
+        <f t="shared" ref="Q34" si="24">P34*N34</f>
         <v>3.3887999999999998</v>
       </c>
-      <c r="R33" s="51"/>
-      <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="46">
-        <f>ROW(B34) - ROW($B$9)</f>
-        <v>25</v>
-      </c>
-      <c r="C34" s="53" t="s">
+      <c r="R34" s="51"/>
+      <c r="S34" s="59"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="46">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D35" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="37" t="s">
+      <c r="E35" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F35" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="G35" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H34" s="37" t="s">
+      <c r="H35" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="I34" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="J34" s="37" t="s">
+      <c r="I35" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="J35" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="K34" s="37" t="s">
+      <c r="K35" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="L34" s="37">
+      <c r="L35" s="37">
         <v>1</v>
       </c>
-      <c r="M34" s="37">
-        <f>L34*5</f>
+      <c r="M35" s="37">
+        <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N34" s="37">
+      <c r="N35" s="37">
         <v>6</v>
       </c>
-      <c r="O34" s="60" t="s">
+      <c r="O35" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="P34" s="38">
+      <c r="P35" s="38">
         <v>0.25240000000000001</v>
       </c>
-      <c r="Q34" s="38">
-        <f>P34*N34</f>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
         <v>1.5144000000000002</v>
       </c>
-      <c r="R34" s="37"/>
-      <c r="S34" s="39"/>
-    </row>
-    <row r="35" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="45"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="82"/>
-      <c r="P35" s="82"/>
-      <c r="Q35" s="48">
-        <f>SUM(Q10:Q34)</f>
-        <v>59.190300000000015</v>
-      </c>
-      <c r="R35" s="77"/>
-      <c r="S35" s="78"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="39"/>
     </row>
     <row r="36" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
       <c r="N36" s="81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O36" s="82"/>
       <c r="P36" s="82"/>
-      <c r="Q36" s="49">
-        <f>Q35/5</f>
-        <v>11.838060000000002</v>
-      </c>
-      <c r="R36" s="79"/>
-      <c r="S36" s="80"/>
+      <c r="Q36" s="48">
+        <f>SUM(Q10:Q35)</f>
+        <v>59.260300000000008</v>
+      </c>
+      <c r="R36" s="77"/>
+      <c r="S36" s="78"/>
+    </row>
+    <row r="37" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="81" t="s">
+        <v>6</v>
+      </c>
+      <c r="O37" s="82"/>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="49">
+        <f>Q36/5</f>
+        <v>11.852060000000002</v>
+      </c>
+      <c r="R37" s="79"/>
+      <c r="S37" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R35:S36"/>
-    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R36:S37"/>
     <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -3338,16 +3412,17 @@
     <hyperlink ref="O29" r:id="rId15"/>
     <hyperlink ref="O30" r:id="rId16"/>
     <hyperlink ref="O31" r:id="rId17"/>
-    <hyperlink ref="O32" r:id="rId18"/>
-    <hyperlink ref="O33" r:id="rId19"/>
-    <hyperlink ref="O34" r:id="rId20"/>
+    <hyperlink ref="O33" r:id="rId18"/>
+    <hyperlink ref="O34" r:id="rId19"/>
+    <hyperlink ref="O35" r:id="rId20"/>
     <hyperlink ref="O14" r:id="rId21"/>
     <hyperlink ref="O17" r:id="rId22"/>
     <hyperlink ref="O24" r:id="rId23"/>
     <hyperlink ref="O19" r:id="rId24"/>
+    <hyperlink ref="O32" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
-  <drawing r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
+  <drawing r:id="rId27"/>
 </worksheet>
 </file>
--- a/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
+++ b/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="187">
   <si>
     <t>Component list</t>
   </si>
@@ -565,6 +565,21 @@
   </si>
   <si>
     <t>4.7K</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>LC-2030C</t>
+  </si>
+  <si>
+    <t>C3011736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shengwei </t>
+  </si>
+  <si>
+    <t>Eternet Cable</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1630,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -3334,65 +3349,121 @@
       <c r="R35" s="37"/>
       <c r="S35" s="39"/>
     </row>
-    <row r="36" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="44"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="81" t="s">
+      <c r="B36" s="46">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I36" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="L36" s="37">
+        <v>1</v>
+      </c>
+      <c r="M36" s="37">
+        <f>L36*5</f>
         <v>5</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="48">
-        <f>SUM(Q10:Q35)</f>
-        <v>59.260300000000008</v>
-      </c>
-      <c r="R36" s="77"/>
-      <c r="S36" s="78"/>
+      <c r="N36" s="37">
+        <v>5</v>
+      </c>
+      <c r="O36" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="P36" s="38">
+        <v>1.3189</v>
+      </c>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
+        <v>6.5945</v>
+      </c>
+      <c r="R36" s="37"/>
+      <c r="S36" s="39"/>
     </row>
     <row r="37" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
       <c r="N37" s="81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37" s="82"/>
       <c r="P37" s="82"/>
-      <c r="Q37" s="49">
-        <f>Q36/5</f>
-        <v>11.852060000000002</v>
-      </c>
-      <c r="R37" s="79"/>
-      <c r="S37" s="80"/>
+      <c r="Q37" s="48">
+        <f>SUM(Q10:Q36)</f>
+        <v>65.854800000000012</v>
+      </c>
+      <c r="R37" s="77"/>
+      <c r="S37" s="78"/>
+    </row>
+    <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="81" t="s">
+        <v>6</v>
+      </c>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="49">
+        <f>Q37/5</f>
+        <v>13.170960000000003</v>
+      </c>
+      <c r="R38" s="79"/>
+      <c r="S38" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R36:S37"/>
-    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R37:S38"/>
     <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N38:P38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -3420,9 +3491,10 @@
     <hyperlink ref="O24" r:id="rId23"/>
     <hyperlink ref="O19" r:id="rId24"/>
     <hyperlink ref="O32" r:id="rId25"/>
+    <hyperlink ref="O36" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
-  <drawing r:id="rId27"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>
--- a/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
+++ b/Design Files/Ethernet-Module-v2.0/BOM/eSpark_BOM_Ethernet-Module-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="186">
   <si>
     <t>Component list</t>
   </si>
@@ -135,9 +135,6 @@
     <t>U1</t>
   </si>
   <si>
-    <t>U2</t>
-  </si>
-  <si>
     <t>X1</t>
   </si>
   <si>
@@ -207,9 +204,6 @@
     <t>SPI LQFP-48(7x7) Ethernet ICs ROHS</t>
   </si>
   <si>
-    <t>TVS DIODE 5.5VWM 8.5VC SOT23-5</t>
-  </si>
-  <si>
     <t>SMD3225-4P Crystals ROHS</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
     <t>48-LQFP (7x7)_</t>
   </si>
   <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
     <t>NX3225GA-25MHZ-STD-CRG-2</t>
   </si>
   <si>
@@ -303,9 +294,6 @@
     <t>W5500</t>
   </si>
   <si>
-    <t>SP0504BAHTG</t>
-  </si>
-  <si>
     <t>Manufacturer</t>
   </si>
   <si>
@@ -396,9 +384,6 @@
     <t>C32843</t>
   </si>
   <si>
-    <t>C10675</t>
-  </si>
-  <si>
     <t>C438901</t>
   </si>
   <si>
@@ -580,6 +565,18 @@
   </si>
   <si>
     <t>Eternet Cable</t>
+  </si>
+  <si>
+    <t>D1, D2</t>
+  </si>
+  <si>
+    <t>TVS DIODE 5.5VWM 8.5VC SOT23-3</t>
+  </si>
+  <si>
+    <t>SP0502BAHTG</t>
+  </si>
+  <si>
+    <t>C207261</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1057,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1222,9 +1219,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1664,15 +1658,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="74"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="73"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1683,7 +1677,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1708,7 +1702,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1722,7 +1716,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="75"/>
+      <c r="S3" s="74"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1733,7 +1727,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1747,7 +1741,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="76"/>
+      <c r="S4" s="75"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1772,7 +1766,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="76"/>
+      <c r="S5" s="75"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1793,7 +1787,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="76"/>
+      <c r="S6" s="75"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1814,7 +1808,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="76"/>
+      <c r="S7" s="75"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1835,7 +1829,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="76"/>
+      <c r="S8" s="75"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1849,49 +1843,49 @@
         <v>17</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>148</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1907,25 +1901,25 @@
         <v>18</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="L10" s="37">
         <v>2</v>
@@ -1938,7 +1932,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P10" s="38">
         <v>3.5200000000000002E-2</v>
@@ -1953,7 +1947,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B34" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B32" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -1963,25 +1957,25 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="L11" s="51">
         <v>7</v>
@@ -1994,7 +1988,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P11" s="52">
         <v>3.5999999999999999E-3</v>
@@ -2019,25 +2013,25 @@
         <v>20</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L12" s="37">
         <v>2</v>
@@ -2050,7 +2044,7 @@
         <v>11</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P12" s="38">
         <v>0.75260000000000005</v>
@@ -2075,25 +2069,25 @@
         <v>21</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L13" s="51">
         <v>2</v>
@@ -2106,7 +2100,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P13" s="52">
         <v>2.8E-3</v>
@@ -2131,23 +2125,23 @@
         <v>22</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="63" t="s">
-        <v>78</v>
+        <v>63</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>75</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2160,7 +2154,7 @@
         <v>50</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P14" s="38">
         <v>1.5800000000000002E-2</v>
@@ -2185,25 +2179,25 @@
         <v>23</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -2216,7 +2210,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P15" s="52">
         <v>7.4000000000000003E-3</v>
@@ -2241,25 +2235,25 @@
         <v>24</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -2272,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P16" s="38">
         <v>4.2299999999999997E-2</v>
@@ -2297,25 +2291,25 @@
         <v>25</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="63" t="s">
-        <v>81</v>
+        <v>63</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>78</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2328,7 +2322,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P17" s="52">
         <v>5.7999999999999996E-3</v>
@@ -2347,32 +2341,30 @@
         <v>9</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>49</v>
+        <v>183</v>
       </c>
       <c r="F18" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="H18" s="37" t="s">
         <v>100</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="37" t="s">
-        <v>157</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="K18" s="37"/>
       <c r="L18" s="37">
         <v>2</v>
       </c>
@@ -2380,805 +2372,799 @@
         <f>L18*5</f>
         <v>10</v>
       </c>
-      <c r="N18" s="37">
-        <v>15</v>
-      </c>
-      <c r="O18" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P18" s="38">
-        <v>0.18790000000000001</v>
-      </c>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="38"/>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>2.8185000000000002</v>
+        <v>0</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64"/>
-      <c r="B19" s="65">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="46">
+        <f>ROW(B19) - ROW($B$9)</f>
+        <v>10</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="L19" s="37">
+        <v>2</v>
+      </c>
+      <c r="M19" s="37">
+        <f>L19*5</f>
+        <v>10</v>
+      </c>
+      <c r="N19" s="37">
+        <v>15</v>
+      </c>
+      <c r="O19" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="P19" s="38">
+        <v>0.18790000000000001</v>
+      </c>
+      <c r="Q19" s="38">
+        <f>P19*N19</f>
+        <v>2.8185000000000002</v>
+      </c>
+      <c r="R19" s="37"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="63"/>
+      <c r="B20" s="64">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C19" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="C20" s="65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="G19" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="H19" s="67" t="s">
-        <v>172</v>
-      </c>
-      <c r="I19" s="67" t="s">
+      <c r="E20" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="66" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>167</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="K20" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="L20" s="66">
+        <v>1</v>
+      </c>
+      <c r="M20" s="66">
+        <f t="shared" ref="M20" si="9">L20*5</f>
+        <v>5</v>
+      </c>
+      <c r="N20" s="66">
+        <v>6</v>
+      </c>
+      <c r="O20" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="P20" s="69">
+        <v>3.47</v>
+      </c>
+      <c r="Q20" s="69">
+        <f t="shared" ref="Q20" si="10">P20*N20</f>
+        <v>20.82</v>
+      </c>
+      <c r="R20" s="66"/>
+      <c r="S20" s="70"/>
+    </row>
+    <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="46">
+        <f>ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="J19" s="67" t="s">
-        <v>157</v>
-      </c>
-      <c r="K19" s="68" t="s">
-        <v>157</v>
-      </c>
-      <c r="L19" s="67">
+      <c r="E21" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="J21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="L21" s="62">
         <v>1</v>
       </c>
-      <c r="M19" s="67">
-        <f t="shared" ref="M19" si="9">L19*5</f>
+      <c r="M21" s="62">
+        <f>L21*5</f>
         <v>5</v>
       </c>
-      <c r="N19" s="67">
-        <v>6</v>
-      </c>
-      <c r="O19" s="69" t="s">
-        <v>173</v>
-      </c>
-      <c r="P19" s="70">
-        <v>3.47</v>
-      </c>
-      <c r="Q19" s="70">
-        <f t="shared" ref="Q19" si="10">P19*N19</f>
-        <v>20.82</v>
-      </c>
-      <c r="R19" s="67"/>
-      <c r="S19" s="71"/>
-    </row>
-    <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="46">
-        <f>ROW(B20) - ROW($B$9)</f>
-        <v>11</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="E20" s="63" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="G20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="I20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="J20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="K20" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="L20" s="63">
-        <v>1</v>
-      </c>
-      <c r="M20" s="63">
-        <f>L20*5</f>
-        <v>5</v>
-      </c>
-      <c r="N20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="O20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="P20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q20" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="R20" s="62" t="s">
-        <v>159</v>
-      </c>
-      <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="47">
+      <c r="N21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="O21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="P21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q21" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="R21" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="47">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="I21" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="J21" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="L21" s="51">
-        <v>1</v>
-      </c>
-      <c r="M21" s="51">
-        <f t="shared" ref="M21" si="11">L21*5</f>
-        <v>5</v>
-      </c>
-      <c r="N21" s="51">
-        <v>20</v>
-      </c>
-      <c r="O21" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P21" s="52">
-        <v>3.3500000000000002E-2</v>
-      </c>
-      <c r="Q21" s="52">
-        <f t="shared" ref="Q21" si="12">P21*N21</f>
-        <v>0.67</v>
-      </c>
-      <c r="R21" s="51"/>
-      <c r="S21" s="59"/>
-    </row>
-    <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="46">
-        <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
       <c r="C22" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="I22" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="J22" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="L22" s="51">
+        <v>1</v>
+      </c>
+      <c r="M22" s="51">
+        <f t="shared" ref="M22" si="11">L22*5</f>
+        <v>5</v>
+      </c>
+      <c r="N22" s="51">
+        <v>20</v>
+      </c>
+      <c r="O22" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="P22" s="52">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="Q22" s="52">
+        <f t="shared" ref="Q22" si="12">P22*N22</f>
+        <v>0.67</v>
+      </c>
+      <c r="R22" s="51"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="46">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="E23" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="L23" s="37">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f>L23*5</f>
+        <v>5</v>
+      </c>
+      <c r="N23" s="37">
+        <v>10</v>
+      </c>
+      <c r="O23" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="P23" s="38">
+        <v>7.3700000000000002E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="R23" s="37"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="47">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="K22" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="L22" s="37">
+      <c r="F24" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="J24" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="K24" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="L24" s="51">
         <v>1</v>
       </c>
-      <c r="M22" s="37">
-        <f>L22*5</f>
+      <c r="M24" s="51">
+        <f t="shared" ref="M24" si="13">L24*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="37">
-        <v>10</v>
-      </c>
-      <c r="O22" s="60" t="s">
+      <c r="N24" s="51">
+        <v>100</v>
+      </c>
+      <c r="O24" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="P24" s="52">
+        <v>1E-3</v>
+      </c>
+      <c r="Q24" s="52">
+        <f t="shared" ref="Q24" si="14">P24*N24</f>
+        <v>0.1</v>
+      </c>
+      <c r="R24" s="51"/>
+      <c r="S24" s="59"/>
+    </row>
+    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="46">
+        <f>ROW(B25) - ROW($B$9)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="P22" s="38">
-        <v>7.3700000000000002E-2</v>
-      </c>
-      <c r="Q22" s="38">
-        <f>P22*N22</f>
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="R22" s="37"/>
-      <c r="S22" s="59"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="47">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="K23" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="L23" s="51">
-        <v>1</v>
-      </c>
-      <c r="M23" s="51">
-        <f t="shared" ref="M23" si="13">L23*5</f>
-        <v>5</v>
-      </c>
-      <c r="N23" s="51">
+      <c r="F25" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="L25" s="37">
+        <v>12</v>
+      </c>
+      <c r="M25" s="37">
+        <f>L25*5</f>
+        <v>60</v>
+      </c>
+      <c r="N25" s="37">
         <v>100</v>
       </c>
-      <c r="O23" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P23" s="52">
-        <v>1E-3</v>
-      </c>
-      <c r="Q23" s="52">
-        <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>0.1</v>
-      </c>
-      <c r="R23" s="51"/>
-      <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="46">
-        <f>ROW(B24) - ROW($B$9)</f>
-        <v>15</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="L24" s="37">
-        <v>12</v>
-      </c>
-      <c r="M24" s="37">
-        <f>L24*5</f>
-        <v>60</v>
-      </c>
-      <c r="N24" s="37">
-        <v>100</v>
-      </c>
-      <c r="O24" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P24" s="52">
+      <c r="O25" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="P25" s="52">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q24" s="38">
-        <f>P24*N24</f>
+      <c r="Q25" s="38">
+        <f>P25*N25</f>
         <v>0.09</v>
       </c>
-      <c r="R24" s="37"/>
-      <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="47">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="E25" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="J25" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="K25" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="L25" s="51">
-        <v>3</v>
-      </c>
-      <c r="M25" s="51">
-        <f t="shared" ref="M25" si="15">L25*5</f>
-        <v>15</v>
-      </c>
-      <c r="N25" s="51">
-        <v>100</v>
-      </c>
-      <c r="O25" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P25" s="52">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q25" s="52">
-        <f t="shared" ref="Q25" si="16">P25*N25</f>
-        <v>0.13</v>
-      </c>
-      <c r="R25" s="51"/>
+      <c r="R25" s="37"/>
       <c r="S25" s="59"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="46">
-        <f>ROW(B26) - ROW($B$9)</f>
+      <c r="B26" s="47">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="L26" s="37">
-        <v>4</v>
-      </c>
-      <c r="M26" s="37">
-        <f>L26*5</f>
-        <v>20</v>
-      </c>
-      <c r="N26" s="37">
+      <c r="D26" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="L26" s="51">
+        <v>3</v>
+      </c>
+      <c r="M26" s="51">
+        <f t="shared" ref="M26" si="15">L26*5</f>
+        <v>15</v>
+      </c>
+      <c r="N26" s="51">
         <v>100</v>
       </c>
       <c r="O26" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P26" s="38">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q26" s="38">
-        <f>P26*N26</f>
-        <v>0.12</v>
-      </c>
-      <c r="R26" s="37"/>
+        <v>153</v>
+      </c>
+      <c r="P26" s="52">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q26" s="52">
+        <f t="shared" ref="Q26" si="16">P26*N26</f>
+        <v>0.13</v>
+      </c>
+      <c r="R26" s="51"/>
       <c r="S26" s="59"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="47">
-        <f t="shared" si="0"/>
+      <c r="B27" s="46">
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="54" t="s">
+      <c r="C27" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="J27" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="K27" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="L27" s="51">
-        <v>1</v>
-      </c>
-      <c r="M27" s="51">
-        <f t="shared" ref="M27" si="17">L27*5</f>
-        <v>5</v>
-      </c>
-      <c r="N27" s="51">
+      <c r="D27" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="L27" s="37">
+        <v>4</v>
+      </c>
+      <c r="M27" s="37">
+        <f>L27*5</f>
+        <v>20</v>
+      </c>
+      <c r="N27" s="37">
         <v>100</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P27" s="52">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="Q27" s="52">
-        <f t="shared" ref="Q27" si="18">P27*N27</f>
-        <v>0.32</v>
-      </c>
-      <c r="R27" s="51"/>
+        <v>153</v>
+      </c>
+      <c r="P27" s="38">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="38">
+        <f>P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="37"/>
       <c r="S27" s="59"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="46">
-        <f>ROW(B28) - ROW($B$9)</f>
+      <c r="B28" s="47">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="L28" s="37">
-        <v>4</v>
-      </c>
-      <c r="M28" s="37">
-        <f>L28*5</f>
-        <v>20</v>
-      </c>
-      <c r="N28" s="37">
+      <c r="D28" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="I28" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="J28" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="K28" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="L28" s="51">
+        <v>1</v>
+      </c>
+      <c r="M28" s="51">
+        <f t="shared" ref="M28" si="17">L28*5</f>
+        <v>5</v>
+      </c>
+      <c r="N28" s="51">
         <v>100</v>
       </c>
       <c r="O28" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P28" s="38">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q28" s="38">
-        <f>P28*N28</f>
-        <v>0.12</v>
-      </c>
-      <c r="R28" s="37"/>
+        <v>153</v>
+      </c>
+      <c r="P28" s="52">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="Q28" s="52">
+        <f t="shared" ref="Q28" si="18">P28*N28</f>
+        <v>0.32</v>
+      </c>
+      <c r="R28" s="51"/>
       <c r="S28" s="59"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="47">
-        <f t="shared" si="0"/>
+      <c r="B29" s="46">
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="I29" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="J29" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="K29" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="L29" s="51">
-        <v>2</v>
-      </c>
-      <c r="M29" s="51">
-        <f t="shared" ref="M29" si="19">L29*5</f>
-        <v>10</v>
-      </c>
-      <c r="N29" s="51">
+      <c r="D29" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="L29" s="37">
+        <v>4</v>
+      </c>
+      <c r="M29" s="37">
+        <f>L29*5</f>
+        <v>20</v>
+      </c>
+      <c r="N29" s="37">
         <v>100</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P29" s="52">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q29" s="52">
-        <f t="shared" ref="Q29" si="20">P29*N29</f>
-        <v>0.11</v>
-      </c>
-      <c r="R29" s="51"/>
+        <v>153</v>
+      </c>
+      <c r="P29" s="38">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q29" s="38">
+        <f>P29*N29</f>
+        <v>0.12</v>
+      </c>
+      <c r="R29" s="37"/>
       <c r="S29" s="59"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="46">
-        <f>ROW(B30) - ROW($B$9)</f>
+      <c r="B30" s="47">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>96</v>
+      <c r="D30" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" s="51" t="s">
+        <v>92</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="L30" s="37">
-        <v>1</v>
-      </c>
-      <c r="M30" s="37">
-        <f>L30*5</f>
-        <v>5</v>
-      </c>
-      <c r="N30" s="37">
+        <v>152</v>
+      </c>
+      <c r="J30" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="K30" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="L30" s="51">
+        <v>2</v>
+      </c>
+      <c r="M30" s="51">
+        <f t="shared" ref="M30" si="19">L30*5</f>
+        <v>10</v>
+      </c>
+      <c r="N30" s="51">
         <v>100</v>
       </c>
       <c r="O30" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P30" s="38">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q30" s="38">
-        <f>P30*N30</f>
-        <v>0.13</v>
-      </c>
-      <c r="R30" s="37"/>
+        <v>153</v>
+      </c>
+      <c r="P30" s="52">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q30" s="52">
+        <f t="shared" ref="Q30" si="20">P30*N30</f>
+        <v>0.11</v>
+      </c>
+      <c r="R30" s="51"/>
       <c r="S30" s="59"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="47">
-        <f t="shared" si="0"/>
+      <c r="B31" s="46">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="51" t="s">
+      <c r="D31" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="H31" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J31" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="K31" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="L31" s="51">
+      <c r="I31" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="L31" s="37">
         <v>1</v>
       </c>
-      <c r="M31" s="51">
-        <f t="shared" ref="M31" si="21">L31*5</f>
+      <c r="M31" s="37">
+        <f>L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="51">
+      <c r="N31" s="37">
         <v>100</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P31" s="52">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q31" s="52">
-        <f t="shared" ref="Q31" si="22">P31*N31</f>
-        <v>0.12</v>
-      </c>
-      <c r="R31" s="51"/>
+        <v>153</v>
+      </c>
+      <c r="P31" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q31" s="38">
+        <f>P31*N31</f>
+        <v>0.13</v>
+      </c>
+      <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="46">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="47">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>96</v>
+      <c r="D32" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H32" s="51" t="s">
+        <v>92</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="L32" s="37">
+        <v>152</v>
+      </c>
+      <c r="J32" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="L32" s="51">
         <v>1</v>
       </c>
-      <c r="M32" s="37">
-        <f>L32*5</f>
+      <c r="M32" s="51">
+        <f t="shared" ref="M32" si="21">L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="37">
+      <c r="N32" s="51">
         <v>100</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P32" s="38">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q32" s="38">
-        <f>P32*N32</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R32" s="37"/>
+        <v>153</v>
+      </c>
+      <c r="P32" s="52">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q32" s="52">
+        <f t="shared" ref="Q32" si="22">P32*N32</f>
+        <v>0.12</v>
+      </c>
+      <c r="R32" s="51"/>
       <c r="S32" s="59"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -3188,31 +3174,31 @@
         <v>24</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="I33" s="51" t="s">
-        <v>157</v>
+        <v>92</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>152</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -3222,75 +3208,75 @@
         <v>5</v>
       </c>
       <c r="N33" s="37">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P33" s="38">
-        <v>2.641</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q33" s="38">
         <f>P33*N33</f>
-        <v>15.846</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R33" s="37"/>
       <c r="S33" s="59"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="47">
-        <f t="shared" si="0"/>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="G34" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="J34" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="K34" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="L34" s="51">
+      <c r="C34" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="I34" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="L34" s="37">
         <v>1</v>
       </c>
-      <c r="M34" s="51">
-        <f t="shared" ref="M34" si="23">L34*5</f>
+      <c r="M34" s="37">
+        <f>L34*5</f>
         <v>5</v>
       </c>
-      <c r="N34" s="51">
+      <c r="N34" s="37">
         <v>6</v>
       </c>
-      <c r="O34" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="P34" s="52">
-        <v>0.56479999999999997</v>
-      </c>
-      <c r="Q34" s="52">
-        <f t="shared" ref="Q34" si="24">P34*N34</f>
-        <v>3.3887999999999998</v>
-      </c>
-      <c r="R34" s="51"/>
+      <c r="O34" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="P34" s="38">
+        <v>2.641</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>15.846</v>
+      </c>
+      <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3303,28 +3289,28 @@
         <v>16</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J35" s="37" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K35" s="37" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="L35" s="37">
         <v>1</v>
@@ -3337,7 +3323,7 @@
         <v>6</v>
       </c>
       <c r="O35" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P35" s="38">
         <v>0.25240000000000001</v>
@@ -3356,31 +3342,31 @@
         <v>27</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I36" s="51" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -3393,7 +3379,7 @@
         <v>5</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P36" s="38">
         <v>1.3189</v>
@@ -3419,17 +3405,17 @@
       <c r="K37" s="45"/>
       <c r="L37" s="45"/>
       <c r="M37" s="45"/>
-      <c r="N37" s="81" t="s">
+      <c r="N37" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="O37" s="82"/>
-      <c r="P37" s="82"/>
+      <c r="O37" s="81"/>
+      <c r="P37" s="81"/>
       <c r="Q37" s="48">
         <f>SUM(Q10:Q36)</f>
-        <v>65.854800000000012</v>
-      </c>
-      <c r="R37" s="77"/>
-      <c r="S37" s="78"/>
+        <v>62.466000000000008</v>
+      </c>
+      <c r="R37" s="76"/>
+      <c r="S37" s="77"/>
     </row>
     <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -3445,17 +3431,17 @@
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
-      <c r="N38" s="81" t="s">
+      <c r="N38" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="O38" s="82"/>
-      <c r="P38" s="82"/>
+      <c r="O38" s="81"/>
+      <c r="P38" s="81"/>
       <c r="Q38" s="49">
         <f>Q37/5</f>
-        <v>13.170960000000003</v>
-      </c>
-      <c r="R38" s="79"/>
-      <c r="S38" s="80"/>
+        <v>12.493200000000002</v>
+      </c>
+      <c r="R38" s="78"/>
+      <c r="S38" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3472,29 +3458,28 @@
     <hyperlink ref="O13" r:id="rId4"/>
     <hyperlink ref="O15" r:id="rId5"/>
     <hyperlink ref="O16" r:id="rId6"/>
-    <hyperlink ref="O18" r:id="rId7"/>
-    <hyperlink ref="O21" r:id="rId8"/>
-    <hyperlink ref="O22" r:id="rId9"/>
-    <hyperlink ref="O23" r:id="rId10"/>
-    <hyperlink ref="O25" r:id="rId11"/>
-    <hyperlink ref="O26" r:id="rId12"/>
-    <hyperlink ref="O27" r:id="rId13"/>
-    <hyperlink ref="O28" r:id="rId14"/>
-    <hyperlink ref="O29" r:id="rId15"/>
-    <hyperlink ref="O30" r:id="rId16"/>
-    <hyperlink ref="O31" r:id="rId17"/>
-    <hyperlink ref="O33" r:id="rId18"/>
-    <hyperlink ref="O34" r:id="rId19"/>
-    <hyperlink ref="O35" r:id="rId20"/>
-    <hyperlink ref="O14" r:id="rId21"/>
-    <hyperlink ref="O17" r:id="rId22"/>
-    <hyperlink ref="O24" r:id="rId23"/>
-    <hyperlink ref="O19" r:id="rId24"/>
-    <hyperlink ref="O32" r:id="rId25"/>
-    <hyperlink ref="O36" r:id="rId26"/>
+    <hyperlink ref="O19" r:id="rId7"/>
+    <hyperlink ref="O22" r:id="rId8"/>
+    <hyperlink ref="O23" r:id="rId9"/>
+    <hyperlink ref="O24" r:id="rId10"/>
+    <hyperlink ref="O26" r:id="rId11"/>
+    <hyperlink ref="O27" r:id="rId12"/>
+    <hyperlink ref="O28" r:id="rId13"/>
+    <hyperlink ref="O29" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O31" r:id="rId16"/>
+    <hyperlink ref="O32" r:id="rId17"/>
+    <hyperlink ref="O34" r:id="rId18"/>
+    <hyperlink ref="O35" r:id="rId19"/>
+    <hyperlink ref="O14" r:id="rId20"/>
+    <hyperlink ref="O17" r:id="rId21"/>
+    <hyperlink ref="O25" r:id="rId22"/>
+    <hyperlink ref="O20" r:id="rId23"/>
+    <hyperlink ref="O33" r:id="rId24"/>
+    <hyperlink ref="O36" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
-  <drawing r:id="rId28"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
+  <drawing r:id="rId27"/>
 </worksheet>
 </file>